--- a/data_extactor/batch_10_fa/batch_0067_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0067_fa.xlsx
@@ -503,17 +503,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Creative Research Systems The Survey System | نرم‌افزار پرونده الکترونیک سلامت EHR | FileMaker Pro | FluidSurveys | Jenzabar EX | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری فرآیندهای پزشکی | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Teams | Microsoft Word | Nebu Dub InterViewer | Oracle PeopleSoft | Qualtrics Insight | نرم‌افزار مصاحبه خودکار RIVS | SAP Business Objects | SaaS SurveyMonkey | نرم‌افزار آماری | نرم‌افزار سیستم‌های اطلاعات دانش‌آموزی SIS | نرم‌افزار مرورگر وب | Zoom</t>
+          <t>Creative Research Systems The Survey System | نرم‌افزار پرونده الکترونیک سلامت EHR | FileMaker Pro | FluidSurveys | Jenzabar EX | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Teams | Microsoft Word | Nebu Dub InterViewer | Oracle PeopleSoft | Qualtrics Insight | نرم‌افزار مصاحبه خودکار RIVS | SAP Business Objects | SaaS SurveyMonkey | نرم‌افزار آماری | نرم‌افزار سیستم‌های اطلاعات دانش‌آموزی SIS | نرم‌افزار مرورگر وب | Zoom</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خوانده شده | نگارش | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | اداری | رایانه‌ها و الکترونیک | ریاضیات | مدیریت و سازماندهی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -523,12 +523,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>تماس با دیگران | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا منظم بودن | اهمیت تکرار وظایف یکسان | صرف زمان به صورت نشسته | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | داخل ساختمان، محیط کنترل‌شده | فشار زمانی | نزدیکی فیزیکی | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای انجام حرکات تکراری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان</t>
+          <t>ارتباط با دیگران | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای انجام حرکات تکراری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارمندان مکاتبات | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط، برنامه‌های دولتی | کارمندان بایگانی | سرپرستان خط مقدم کارکنان پشتیبانی اداری و دفتری | فناوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | کارمندان پردازش بیمه و خسارت | تحلیلگران مدیریت | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری، عمومی | نمایندگان بیمار | کارمندان حقوق و دستمزد و ثبت زمان | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی | دستیاران آماری | پژوهشگران نظرسنجی</t>
+          <t>کارمندان مکاتبات | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | کارمندان بایگانی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | متخصصان منابع انسانی | کارمندان پردازش بیمه و بیمه‌نامه | تحلیل‌گران مدیریت | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری عمومی | نمایندگان بیمار | کارمندان حقوق و دستمزد و ثبت زمان | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران تحقیقات علوم اجتماعی | دستیاران آماری | پژوهشگران نظرسنجی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,17 +560,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe Photoshop | سیستم‌های خودکار امانت | C++ | نرم‌افزار فهرست‌نویسی | نرم‌افزار پایگاه داده | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Windows | Microsoft Word | پایگاه‌های داده Online Computer Library Center (OCLC) | نرم‌افزار بایگانی سوابق | ResourceMate Plus | سیستم‌های بازیابی ویدیو | نرم‌افزار مرورگر وب | WorldCat</t>
+          <t>Adobe Acrobat | Adobe Photoshop | سیستم‌های خودکار امانت | C++ | نرم‌افزار فهرست‌نویسی | نرم‌افزار پایگاه داده | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Windows | Microsoft Word | پایگاه‌های داده Online Computer Library Center (OCLC) | نرم‌افزار ثبت سوابق | ResourceMate Plus | سیستم‌های بازیابی ویدیو | نرم‌افزار مرورگر وب | WorldCat</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب خوانده شده | تفکر انتقادی | سخن گفتن | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | اداری | زبان انگلیسی | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -580,12 +580,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | تماس با دیگران | داخل ساختمان، محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>آرشیویست‌ها | کارمندان مکاتبات | موزه‌داران | متخصصان مدیریت اسناد | ویراستاران | معلمان دبستان، به جز آموزش استثنایی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | مدرسان علوم کتابداری، پس از متوسطه | کاردان‌های کتابداری | تحلیلگران مدیریت | کارمندان دفتری، عمومی | اپراتورهای ماشین‌های اداری، به جز رایانه | نمونه‌خوان‌ها و کپی‌نویسان | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی | انبارداران و پرکنندگان سفارش</t>
+          <t>آرشیوچی‌ها | کارمندان مکاتبات | موزه‌داران | متخصصان مدیریت اسناد | ویراستاران | معلمان دبستان، به استثنای آموزش استثنایی | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | هماهنگ‌کنندگان آموزشی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | مدرسان علوم کتابداری، آموزش عالی | تکنسین‌های کتابخانه | تحلیل‌گران مدیریت | کارمندان دفتری عمومی | اپراتورهای ماشین‌های اداری، به جز رایانه | مصححان و نشانه‌گذاران کپی | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران تحقیقات علوم اجتماعی | قفسه‌چین‌ها و پرکننده‌های سفارش</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خوانده شده | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | اداری | رایانه‌ها و الکترونیک | قانون و حکومت | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | قانون و دولت | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | استدلال ریاضی | سهولت در کار با اعداد | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | استدلال ریاضی | توانایی عددی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | تماس با دیگران | داخل ساختمان، محیط کنترل‌شده | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت دقیق یا منظم بودن | صرف زمان به صورت نشسته | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ایمیل | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | پیامدهای کاری و نتایج سایر کارکنان</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ایمیل | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور فاکتور و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتباری | مصاحبه‌کنندگان واجد شرایط، برنامه‌های دولتی | بازرسان مالی | مدیران مالی | کارمندان پردازش بیمه و خسارت | پذیره‌نویسان بیمه | افسران وام | کارمندان حساب‌های جدید | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | بازرسان و وصول‌کنندگان مالیات، و مأموران درآمد | تهیه‌کنندگان اظهارنامه مالیاتی | تحویلداران بانک | بازرسان اسناد، خلاصه‌نویسان و جستجوگران اسناد</t>
+          <t>وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان مالی | مدیران مالی | کارمندان پردازش بیمه و بیمه‌نامه | بیمه‌گران | مسئولان وام | کارمندان حساب‌های جدید | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تهیه‌کنندگان اظهارنامه مالیاتی | تحویل‌داران | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب خوانده شده | تفکر انتقادی | نظارت | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | بازاریابی و فروش | اداری | زبان انگلیسی | رایانه‌ها و الکترونیک | ریاضیات | اقتصاد و حسابداری | ایمنی و امنیت عمومی | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | اداری | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | تماس با دیگران | ایمیل | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا منظم بودن | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت تکرار وظایف یکسان | داخل ساختمان، محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور فاکتور و ثبت | کارمندان دفترداری, حسابداری و حسابرسی | کارمندان کارگزاری | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتباری | نمایندگان خدمات مشتریان | مدیران مالی | تحلیلگران مالی و سرمایه‌گذاری | کارمندان پردازش بیمه و خسارت | نمایندگان فروش بیمه | مصاحبه‌کنندگان و کارمندان وام | افسران وام | کارمندان دفتری، عمومی | مشاوران مالی شخصی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالا و خدمات مالی | بازاریابان تلفنی | تحویلداران بانک</t>
+          <t>وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | نمایندگان خدمات مشتریان | مدیران مالی | تحلیلگران مالی و سرمایه‌گذاری | کارمندان پردازش بیمه و بیمه‌نامه | نمایندگان فروش بیمه | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | کارمندان دفتری عمومی | مشاوران مالی شخصی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازاریابان تلفنی | تحویل‌داران</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خوانده شده | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | تولید و فرآوری | رایانه‌ها و الکترونیک | آموزش و پرورش | زبان انگلیسی | اداری | ریاضیات | بازاریابی و فروش | حمل و نقل | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مدیریت و سازماندهی | مهندسی و فناوری</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری | رایانه و الکترونیک | آموزش و پرورش | زبان انگلیسی | اداری | ریاضیات | فروش و بازاریابی | حمل و نقل | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مدیریت و اداره | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده | ایمیل | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | صرف زمان به صورت نشسته | فشار زمانی | اهمیت دقیق یا منظم بودن | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | صرف زمان برای نشستن | فشار زمانی | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | کارمندان صدور فاکتور و ثبت | صندوقداران | کارمندان مکاتبات | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | رانندگان/کارکنان فروش | سرپرستان خط مقدم کارکنان فروش غیرخرده‌فروشی | کارمندان پست و اپراتورهای ماشین‌های پستی، به جز خدمات پستی | کارمندان دفتری، عمومی | کارمندان خدمات پستی | روسای پست و مدیران پست | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و تسریع | مأموران خرید، به جز محصولات عمده‌فروشی، خرده‌فروشی و کشاورزی | مدیران خرید | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | کارمندان ارسال، دریافت و موجودی | انبارداران و پرکنندگان سفارش | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
+          <t>نمایندگان فروش تبلیغات | کارمندان صدور صورتحساب و ثبت | صندوق‌داران | کارمندان مکاتبات | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | رانندگان توزیع و فروشندگان | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | کارمندان دفتری عمومی | کارمندان خدمات پستی | رئیس پست و سرپرستان پست | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و هماهنگی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,17 +788,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ADP Enterprise HR | ADP Workforce Now | نرم‌افزار ردیابی متقاضی | Blackboard Learn | Blackboard Learning System | Corel WordPerfect Office Suite | نرم‌افزار پایگاه داده | نرم‌افزار سیستم مدیریت اسناد | نرم‌افزار ایمیل | سیستم مدیریت عملکرد کارکنان | نرم‌افزار خودخدمتی کارکنان | FileMaker Pro | Google Calendar | Google Docs | سیستم اطلاعات منابع انسانی HRIS | نرم‌افزار مدیریت منابع انسانی HRMS | سیستم مدیریت یادگیری LMS | LinkedIn | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Oracle HRIS | Oracle PeopleSoft | Oracle PeopleSoft Enterprise Employee Self-Service | Oracle PeopleSoft Enterprise Human Resources | Oracle Self-Service Human Resources | Oracle Taleo | SAP ERP | نرم‌افزار اسکن | Ultimate Software UltiPro Workplace | Workscape HR Service Center</t>
+          <t>ADP Enterprise HR | ADP Workforce Now | نرم‌افزار ردیابی متقاضی | Blackboard Learn | Blackboard Learning System | Corel WordPerfect Office Suite | نرم‌افزار پایگاه داده | نرم‌افزار سیستم مدیریت اسناد | نرم‌افزار ایمیل | سیستم مدیریت عملکرد کارکنان | نرم‌افزار سلف‌سرویس کارکنان | FileMaker Pro | Google Calendar | Google Docs | سیستم اطلاعات منابع انسانی (HRIS) | نرم‌افزار مدیریت منابع انسانی HRMS | سیستم مدیریت یادگیری LMS | LinkedIn | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Oracle HRIS | Oracle PeopleSoft | Oracle PeopleSoft Enterprise Employee Self-Service | Oracle PeopleSoft Enterprise Human Resources | Oracle Self-Service Human Resources | Oracle Taleo | SAP ERP | نرم‌افزار اسکن | Ultimate Software UltiPro Workplace | Workscape HR Service Center</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب خوانده شده | سخن گفتن | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پرسنل و منابع انسانی | اداری | خدمات مشتریان و شخصی | مدیریت و سازماندهی | زبان انگلیسی</t>
+          <t>پرسنل و منابع انسانی | اداری | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | تماس با دیگران | اهمیت دقیق یا منظم بودن | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت تکرار وظایف یکسان | فشار زمانی | صرف زمان به صورت نشسته | تعیین وظایف، اولویت‌ها و اهداف | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | داخل ساختمان، محیط کنترل‌شده | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>ایمیل | مکالمات تلفنی | ارتباط با دیگران | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت تکرار وظایف یکسان | فشار زمانی | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | محیط داخلی، دارای کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تجزیه و تحلیل شغل | مصاحبه‌کنندگان واجد شرایط، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان خط مقدم کارکنان فروش غیرخرده‌فروشی | سرپرستان خط مقدم کارکنان پشتیبانی اداری و دفتری | فناوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | مدیران منابع انسانی | متخصصان منابع انسانی | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | متخصصان روابط کار | تحلیلگران مدیریت | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری، عمومی | کارمندان حقوق و دستمزد و ثبت زمان | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | مدیران خدمات اجتماعی و جامعه</t>
+          <t>مدیران خدمات اداری | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | منشی‌های اجرایی و دستیاران اداری اجرایی | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | مدیران منابع انسانی | متخصصان منابع انسانی | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | متخصصان روابط کار | تحلیل‌گران مدیریت | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری عمومی | کارمندان حقوق و دستمزد و ثبت زمان | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | مدیران خدمات اجتماعی و جامعه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,17 +845,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3M Post-it App | Alpha Software Alpha Five | نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار سیستم اطلاعات خودکار | نرم‌افزار صدور فاکتور | Blackbaud The Raiser's Edge | نرم‌افزار دفترداری | نرم‌افزار سیستم پردازش خسارت | Corel WordPerfect Office Suite | نرم‌افزار ورود داده‌ها | نرم‌افزار پایگاه داده | نرم‌افزار مدیریت تقویم الکترونیکی | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار ایمیل | FileMaker Pro | نرم‌افزار سیستم بایگانی | GE Healthcare Centricity EMR | Google Docs | Google Drive | HMS | IBM Check Processing Control System CPSC | IBM Notes | Intrado SchoolMessenger | Intuit QuickBooks | Kodak Dental Systems Kodak SOFTDENT Practice management software PMS | McKesson Lytec | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری فرآیندهای پزشکی | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint Server | Microsoft Windows | Microsoft Word | St. Paul Travelers e-CARMA | نرم‌افزار مرورگر وب</t>
+          <t>3M Post-it App | Alpha Software Alpha Five | نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار سیستم اطلاعات خودکار | نرم‌افزار صدور صورتحساب | Blackbaud The Raiser's Edge | نرم‌افزار حسابداری | نرم‌افزار سیستم پردازش خسارت | Corel WordPerfect Office Suite | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار مدیریت تقویم الکترونیکی | نرم‌افزار پرونده الکترونیک سلامت EHR | نرم‌افزار ایمیل | FileMaker Pro | نرم‌افزار سیستم بایگانی | GE Healthcare Centricity EMR | Google Docs | Google Drive | HMS | IBM Check Processing Control System CPSC | IBM Notes | Intrado SchoolMessenger | Intuit QuickBooks | Kodak Dental Systems Kodak SOFTDENT Practice management software PMS | McKesson Lytec | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint Server | Microsoft Windows | Microsoft Word | St. Paul Travelers e-CARMA | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب خوانده شده | تفکر انتقادی | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | اداری | زبان انگلیسی | رایانه‌ها و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | تماس با دیگران | فراوانی تصمیم‌گیری | ایمیل | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، محیط کنترل‌شده | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان به صورت نشسته | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | اهمیت دقیق یا منظم بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | فراوانی تصمیم‌گیری | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارمندان صدور فاکتور و ثبت | صندوقداران | کارمندان مکاتبات | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | سرپرستان خط مقدم کارکنان پشتیبانی اداری و دفتری | کارمندان میز هتل، متل و اقامتگاه | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | منشی‌های حقوقی و دستیاران اداری | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری، عمومی | نمایندگان بیمار | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | اپراتورهای تلفنخانه، شامل خدمات پاسخگویی | بازاریابان تلفنی</t>
+          <t>مدیران خدمات اداری | کارمندان صدور صورتحساب و ثبت | صندوق‌داران | کارمندان مکاتبات | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | کارمندان پذیرش هتل، متل و اقامتگاه | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | منشی‌های حقوقی و دستیاران اداری | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | کارمندان دفتری عمومی | نمایندگان بیمار | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | بازاریابان تلفنی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب خوانده شده | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | رایانه‌ها و الکترونیک | ایمنی و امنیت عمومی | حمل و نقل | جغرافیا | روانشناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | ایمنی و امنیت عمومی | حمل و نقل | جغرافیا | روان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>تماس با دیگران | اهمیت تکرار وظایف یکسان | داخل ساختمان، محیط کنترل‌شده | اهمیت دقیق یا منظم بودن | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | فراوانی تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | موقعیت‌های تعارض | میزان خودکارسازی | صرف زمان برای انجام حرکات تکراری</t>
+          <t>ارتباط با دیگران | اهمیت تکرار وظایف یکسان | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | آزادی در تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | موقعیت‌های تعارض | میزان خودکارسازی | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متخصصان عملیات فرودگاه | باربران چمدان و پادوها | رانندگان اتوبوس، ترانزیت و بین‌شهری | نمایندگان بار و محموله | دربان‌ها | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | دیسپچرهار، به جز پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط مقدم همراهان مسافر | مهمانداران هواپیما | متصدیان حمل و نقل کالا | کارمندان میز هتل، متل و اقامتگاه | همراهان مسافر | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | رانندگان شاتل و شوفرها | غربالگران امنیت حمل و نقل | نمایندگان مسافرتی | راهنمایان سفر | راهنماها، متصدیان لابی و بلیط‌گیرها</t>
+          <t>متخصصان عملیات فرودگاه | باربران چمدان و پادوهای هتل | رانندگان اتوبوس، ترانزیت و بین‌شهری | نمایندگان بار و محموله | کانسرج‌ها | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول مهمانداران مسافری | مهمانداران هواپیما | متصدیان حمل و نقل | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان مسافران | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | رانندگان شاتل و شوفرها | غربالگران امنیتی حمل و نقل | آژانس‌های مسافرتی | راهنمایان سفر | راهنماها، متصدیان لابی و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | Microsoft Access | Microsoft SharePoint | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه گسترده | Adobe Acrobat</t>
+          <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | Microsoft Access | Microsoft SharePoint | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه‌گسترده | Adobe Acrobat</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خوانده شده | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | مدیریت و سازماندهی | رایانه‌ها و الکترونیک | قانون و حکومت | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | قانون و دولت | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | چالاکی انگشتان | چالاکی دست | بینایی دور | حفظ کردن | روان بودن ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، محیط کنترل‌شده | صرف زمان به صورت نشسته | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا منظم بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارمندان بایگانی | کارمندان مکاتبات | کارمندان ثبت سفارش | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان خدمات مشتریان | کارمندان دادگاه، شهرداری و مجوز | مصاحبه‌کنندگان واجد شرایط، برنامه‌های دولتی | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | دستیاران کتابخانه، دفتری | کارمندان میز هتل، متل و اقامتگاه | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | کاربران ورود داده‌ها | کارمندان دفتری، عمومی | متخصصان مدارک پزشکی | متخصصان مدیریت اسناد | کارمندان پردازش بیمه و خسارت | دستیاران آماری | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | سرپرستان خط مقدم کارکنان پشتیبانی اداری و دفتری</t>
+          <t>کارمندان بایگانی | کارمندان مکاتبات | کارمندان ثبت سفارش | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان خدمات مشتریان | کارمندان دادگاه، شهرداری و مجوز | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | دستیاران کتابخانه، دفتری | کارمندان پذیرش هتل، متل و اقامتگاه | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | اپراتورهای ورود داده | کارمندان دفتری عمومی | متخصصان مدارک پزشکی | متخصصان مدیریت اسناد | کارمندان پردازش بیمه و بیمه‌نامه | دستیاران آماری | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,17 +1016,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار کارگزاری | Corel WordPerfect Office Suite | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ثبت اطلاعات | نرم‌افزار SAP | نرم‌افزار مدیریت حمل و نقل | نرم‌افزار سیستم مدیریت حمل و نقل TMS | نرم‌افزار مرورگر وب | نرم‌افزار دیسپچ مبتنی بر وب</t>
+          <t>نرم‌افزار کارگزاری | Corel WordPerfect Office Suite | نرم‌افزار پایگاه داده | نرم‌افزار ایمیل | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار ثبت اطلاعات | نرم‌افزار SAP | نرم‌افزار مدیریت حمل و نقل | نرم‌افزار سیستم مدیریت حمل‌ونقل TMS | نرم‌افزار مرورگر وب | نرم‌افزار دیسپچ مبتنی بر وب</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب خوانده شده | نظارت | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>حمل و نقل | جغرافیا | ایمنی و امنیت عمومی | زبان انگلیسی | مدیریت و سازماندهی | آموزش و پرورش | قانون و حکومت | مخابرات | اداری | خدمات مشتریان و شخصی | ارتباطات و رسانه</t>
+          <t>حمل و نقل | جغرافیا | ایمنی و امنیت عمومی | زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | قانون و دولت | مخابرات | اداری | خدمات مشتری و شخصی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به صورت نشسته | ایمیل | آزادی در تصمیم‌گیری | فشار زمانی | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای نشستن | ایمیل | آزادی در تصمیم‌گیری | فشار زمانی | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>سرپرستان جابجایی بار هواپیما | پیک‌ها و نامه‌رسان‌ها | کارگزاران گمرک | دیسپچرهار، به جز پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط مقدم اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | متصدیان حمل و نقل کالا | رانندگان کامیون‌های سنگین و تریلی | رانندگان کامیون‌های سبک | متخصصان لجستیک | تحلیلگران لجستیک | کارمندان ثبت سفارش | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | مرتب‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش پست خدمات پستی | مأموران خرید، به جز محصولات عمده‌فروشی، خرده‌فروشی و کشاورزی | لوکوموتیورانان و مسئولان ایستگاه راه‌آهن | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | کارمندان ارسال، دریافت و موجودی | بازرسان حمل و نقل | مدیران حمل و نقل، انبارداری و توزیع</t>
+          <t>سرپرستان جابجایی بار هواپیما | پیک‌ها و نامه‌رسان‌ها | کارگزاران گمرک | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | متصدیان حمل و نقل | رانندگان کامیون‌های سنگین و تریلی | رانندگان کامیون‌های سبک | لجستیسین‌ها | تحلیلگران لجستیک | کارمندان ثبت سفارش | کارمندان خدمات پستی | نامه‌رسان‌های خدمات پستی | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | رئیس قطارها و مدیران محوطه راه‌آهن | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | کارمندان ارسال، دریافت و موجودی کالا | بازرسان حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0067_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0067_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری | رایانه و الکترونیک | ریاضیات | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | دید نزدیک | مرتب‌سازی اطلاعات | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان مکاتبات اداری | کارشناسان خدمات مشتریان | مصاحبه‌گران تعیین صلاحیت برنامه‌های دولتی | متصدیان بایگانی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | متخصصان اطلاعات سلامت و ثبت داده‌های پزشکی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | متخصصان منابع انسانی | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه‌ای | تحلیل‌گران مدیریت | متخصصان اسناد و مدارک پزشکی | منشی‌ها و دستیاران اداری پزشکی | متصدیان امور دفتری، عمومی | نمایندگان پیگیری امور بیماران | کارشناسان حقوق، دستمزد و ثبت ساعات کار | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی | دستیاران آمار | پژوهشگران پیمایشی و افکارسنجی</t>
+          <t>کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | متصدیان بایگانی و اسناد | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان منابع انسانی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان امور دفتری و امور عمومی اداری | کارشناسان امور بیماران و پذیرش | کارمندان امور حقوق، دستمزد و ثبت زمان | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | دستیاران و تکنسین‌های آمار | پژوهشگران پیمایشی و افکارسنجی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | امور اداری | زبان انگلیسی | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | درک شفاهی | دید نزدیک | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در دسته‌بندی | بیان کتبی</t>
+          <t>درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | درک شفاهی | بینایی نزدیک | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>آرشیوپژوهان و کارشناسان اسناد تاریخی | کارشناسان مکاتبات اداری | موزه‌داران | متخصصان مدیریت اسناد | ویراستاران | معلمان دوره ابتدایی، به جز آموزش استثنایی | منشی‌ها و دستیاران اجرایی مدیریت | متصدیان بایگانی | هماهنگ‌کنندگان برنامه‌های آموزشی | کتابداران و متخصصان مجموعه‌های چندرسانه‌ای | مدرسان کتابداری آموزش عالی | تکنسین‌های کتابداری | تحلیل‌گران مدیریت | متصدیان امور دفتری، عمومی | اپراتورهای ماشین‌های اداری، به جز رایانه | مصححان و نمونه‌خوان‌ها | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | دستیاران پژوهشی علوم اجتماعی | کارگران چیدمان و آماده‌سازی سفارش</t>
+          <t>کارشناسان اسناد و آرشیو | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | موزه‌داران | کارشناسان مدیریت اسناد و مدارک | ویراستاران | معلمان دوره ابتدایی، به‌جز آموزش استثنایی | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌های کتابداری | کارشناسان تحلیل مدیریت و روش‌ها | متصدیان امور دفتری و امور عمومی اداری | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | ویراستاران فنی و نمونه‌خوان‌ها | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | متصدیان چیدمان و آماده‌سازی سفارش</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری | رایانه و الکترونیک | حقوق و امور دولتی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | رایانه و الکترونیک | قانون و دولت | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | استدلال ریاضی | توانایی کار با اعداد | انعطاف‌پذیری در دسته‌بندی | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | استدلال ریاضی | توانایی عددی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ماموران وصول مطالبات و حساب‌ها | کارشناسان صدور صورت‌حساب و ثبت اسناد | کارشناسان دفترداری، حسابداری و حسابرسی | کارگزاران بورس و اوراق بهادار | تحلیل‌گران اعتبار | متصدیان بررسی، تایید و پرونده‌های اعتبار | مشاوران اعتباری | مصاحبه‌گران تعیین صلاحیت برنامه‌های دولتی | ارزیابان مالی | مدیران مالی | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه‌ای | کارشناسان صدور و ارزیابی بیمه | کارشناسان اعطای تسهیلات | کارشناسان افتتاح حساب | مشاوران مالی شخصی | کارگزاران و نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | ممیزان و ماموران مالیاتی | تنظیم‌کنندگان اظهارنامه مالیاتی | تحویل‌داران | کارشناسان بررسی و استعلام اسناد مالکیت</t>
+          <t>کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | بازرسان و ارزیابان مالی | مدیران امور مالی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان افتتاح حساب | مشاوران مالی فردی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | تحویل‌داران و متصدیان امور بانکی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | امور اداری | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری | ایمنی و امنیت عمومی | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | اداری | زبان انگلیسی | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت به مسئله | استدلال ریاضی | بیان کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | تشخیص گفتار | وضوح گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله | استدلال ریاضی | بیان کتبی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ماموران وصول مطالبات و حساب‌ها | کارشناسان صدور صورت‌حساب و ثبت اسناد | کارشناسان دفترداری، حسابداری و حسابرسی | کارگزاران بورس و اوراق بهادار | تحلیل‌گران اعتبار | متصدیان بررسی، تایید و پرونده‌های اعتبار | مشاوران اعتباری | کارشناسان خدمات مشتریان | مدیران مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه‌ای | نمایندگان فروش بیمه | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان اعطای تسهیلات | متصدیان امور دفتری، عمومی | مشاوران مالی شخصی | کارشناسان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و گردشگری | کارگزاران و نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | کارشناسان بازاریابی تلفنی | تحویل‌داران</t>
+          <t>کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان خدمات و پشتیبانی مشتریان | مدیران امور مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان پردازش خسارت و بیمه‌نامه‌ها | نمایندگان و کارشناسان فروش بیمه | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان امور دفتری و امور عمومی اداری | مشاوران مالی فردی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارشناسان بازاریابی تلفنی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید و فرآوری | رایانه و الکترونیک | آموزش و تدریس | زبان انگلیسی | امور اداری | ریاضیات | فروش و بازاریابی | حمل‌ونقل | ایمنی و امنیت عمومی | پرسنلی و منابع انسانی | مدیریت و امور اداری | مهندسی و فناوری</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری | رایانه و الکترونیک | آموزش و پرورش | زبان انگلیسی | اداری | ریاضیات | فروش و بازاریابی | حمل و نقل | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | مدیریت و اداره | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | تشخیص گفتار | درک شفاهی | بیان شفاهی | وضوح گفتار | درک کتبی | حساسیت به مسئله | بیان کتبی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | سرعت ادراک | انعطاف‌پذیری در دسته‌بندی | توجه انتخابی | انعطاف‌پذیری در جمع‌بندی</t>
+          <t>بینایی نزدیک | تشخیص گفتار | درک شفاهی | بیان شفاهی | وضوح گفتار | درک کتبی | حساسیت به مسئله | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | کارشناسان صدور صورت‌حساب و ثبت اسناد | صندوق‌داران | کارشناسان مکاتبات اداری | کارشناسان پیشخوان و اجاره | کارشناسان خدمات مشتریان | رانندگان توزیع و فروش | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | کارمندان امور پست و اپراتورهای ماشین‌های پستی، به جز پست دولتی | متصدیان امور دفتری، عمومی | کارمندان خدمات پستی | روسای پست و سرپرستان توزیع مرسولات پستی | کارشناسان تدارکات و خرید | کارشناسان برنامه‌ریزی، تولید و پیگیری | کارشناسان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | کارشناسان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و گردشگری | کارمندان بارگیری، تحویل‌گیری و انبارداری | کارگران چیدمان و آماده‌سازی سفارش | خریداران عمده و خرد، به جز محصولات کشاورزی</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | کارمندان صدور صورتحساب و ثبت اسناد مالی | صندوق‌داران | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | رانندگان توزیع و فروش مویرگی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | متصدیان امور دفتری و امور عمومی اداری | متصدیان باجه و امور پستی | مدیران و رؤسای دفاتر پستی | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | تفکر انتقادی | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | امور اداری | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی</t>
+          <t>پرسنل و منابع انسانی | اداری | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | دید نزدیک | تشخیص گفتار | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بیان کتبی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | مدیران جبران خدمت و مزایا | متخصصان جبران خدمت، مزایا و تجزیه و تحلیل شغل | مصاحبه‌گران تعیین صلاحیت برنامه‌های دولتی | منشی‌ها و دستیاران اجرایی مدیریت | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | متخصصان اطلاعات سلامت و ثبت داده‌های پزشکی | مدیران منابع انسانی | متخصصان منابع انسانی | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | متخصصان روابط کار | تحلیل‌گران مدیریت | متخصصان اسناد و مدارک پزشکی | منشی‌ها و دستیاران اداری پزشکی | متصدیان امور دفتری، عمومی | کارشناسان حقوق، دستمزد و ثبت ساعات کار | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | مدیران خدمات اجتماعی و عمومی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | مسئولان دفاتر و دستیاران اجرایی مدیریت | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | مدیران منابع انسانی | کارشناسان منابع انسانی | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | کارشناسان روابط کار و امور تشکل‌های کارگری | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان امور دفتری و امور عمومی اداری | کارمندان امور حقوق، دستمزد و ثبت زمان | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | امور اداری | زبان انگلیسی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | اداری | زبان انگلیسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | دید نزدیک | توجه انتخابی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارشناسان صدور صورت‌حساب و ثبت اسناد | صندوق‌داران | کارشناسان مکاتبات اداری | کارشناسان پیشخوان و اجاره | کارشناسان خدمات مشتریان | منشی‌ها و دستیاران اجرایی مدیریت | متصدیان بایگانی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | متصدیان پذیرش هتل، متل و اقامتگاه | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | منشی‌ها و دستیاران اداری حقوقی | متخصصان اسناد و مدارک پزشکی | منشی‌ها و دستیاران اداری پزشکی | متصدیان امور دفتری، عمومی | نمایندگان پیگیری امور بیماران | کارشناسان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و گردشگری | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | اپراتورهای تلفنخانه، شامل خدمات پاسخ‌گویی | کارشناسان بازاریابی تلفنی</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارمندان صدور صورتحساب و ثبت اسناد مالی | صندوق‌داران | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان امور دفتری و امور عمومی اداری | کارشناسان امور بیماران و پذیرش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | منشی‌ها و دستیاران اداری عمومی | اپراتورهای مراکز تلفن و پاسخگویی | کارشناسان بازاریابی تلفنی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | ایمنی و امنیت عمومی | حمل‌ونقل | جغرافیا | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | ایمنی و امنیت عمومی | حمل و نقل | جغرافیا | روان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | دید نزدیک | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی</t>
+          <t>بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال قیاسی | حساسیت به مسئله | بیان کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متخصصان عملیات فرودگاهی | باربران هتل و حمل‌کنندگان چمدان | رانندگان اتوبوس‌های درون‌شهری و بین‌شهری | کارگزاران حمل‌ونقل و بار | کارشناسان راهنمای مقیم هتل (کانسیرژ) | کارشناسان پیشخوان و اجاره | کارشناسان خدمات مشتریان | دیسپچرهای ناوگان حمل‌ونقل، به جز پلیس، آتش‌نشانی و اورژانس | سرپرستان رده‌اول خدمه مسافری | مهمانداران هواپیما | کارگزاران ترابری و حمل‌ونقل کالا (فورواردری) | متصدیان پذیرش هتل، متل و اقامتگاه | مهمانداران و خدمه مسافری | متصدیان پذیرش و اطلاعات | کارشناسان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و گردشگری | رانندگان سرویس و تشریفات | بازرسان و ماموران بازرسی امنیت مسافران | مدیران فنی و دفاتر خدمات مسافرتی | راهنمایان تور و گردشگری | راهنمایان سالن، متصدیان لابی و کنترل‌کنندگان بلیت</t>
+          <t>کارشناسان عملیات فرودگاهی | متصدیان حمل بار و خدمات هتل | رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | کارگزاران حمل‌ونقل و بار | متصدیان تشریفات و خدمات میهمانان | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول مهمانداران و خدمه مسافری | مهمانداران هواپیما | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | مهمانداران و متصدیان خدمات مسافران | متصدیان پذیرش و اطلاعات | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | رانندگان خودروهای سرویس و تشریفات | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | کارشناسان و دفاتر خدمات مسافرتی و جهانگردی | راهنمایان گردشگری و تور | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | حقوق و امور دولتی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | قانون و دولت | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | اشتراک زمانی | چابکی انگشتان | چابکی دستی | دید دور | به‌خاطرسپاری | روانی ایده‌ها | سرعت ادراک | انعطاف‌پذیری در جمع‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان بایگانی | کارشناسان مکاتبات اداری | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان پذیرش و اطلاعات | کارشناسان خدمات مشتریان | متصدیان دفاتر خدمات قضایی، شهرداری و صدور مجوزها | مصاحبه‌گران تعیین صلاحیت برنامه‌های دولتی | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | کمک‌کتابداران دفتری | متصدیان پذیرش هتل، متل و اقامتگاه | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | اپراتورهای ورود اطلاعات | متصدیان امور دفتری، عمومی | متخصصان اسناد و مدارک پزشکی | متخصصان مدیریت اسناد | کارشناسان پردازش پرونده‌ها و خسارت‌های بیمه‌ای | دستیاران آمار | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی</t>
+          <t>متصدیان بایگانی و اسناد | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان پذیرش و اطلاعات | کارشناسان خدمات و پشتیبانی مشتریان | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | کمک‌کتابداران دفتری | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان امور دفتری و امور عمومی اداری | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | کارشناسان مدیریت اسناد و مدارک | کارمندان پردازش خسارت و بیمه‌نامه‌ها | دستیاران و تکنسین‌های آمار | منشی‌ها و دستیاران اداری عمومی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | نظارت | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | جغرافیا | ایمنی و امنیت عمومی | زبان انگلیسی | مدیریت و امور اداری | آموزش و تدریس | حقوق و امور دولتی | مخابرات و ارتباطات | امور اداری | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه</t>
+          <t>حمل و نقل | جغرافیا | ایمنی و امنیت عمومی | زبان انگلیسی | مدیریت و اداره | آموزش و پرورش | قانون و دولت | مخابرات | اداری | خدمات مشتری و شخصی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | دید نزدیک | حساسیت به مسئله | بیان کتبی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | بینایی نزدیک | حساسیت به مسئله | بیان کتبی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>سرپرستان جابه‌جایی بار هواپیما | نامه‌رسان‌ها و پیک‌ها | کارگزاران گمرکی (حق‌العمل‌کاران گمرک) | دیسپچرهای ناوگان حمل‌ونقل، به جز پلیس، آتش‌نشانی و اورژانس | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | کارگزاران ترابری و حمل‌ونقل کالا (فورواردری) | رانندگان تریلرها و کامیون‌های سنگین | رانندگان خودروهای باری سبک | کارشناسان ارشد لجستیک | تحلیل‌گران لجستیک و زنجیره تامین | متصدیان ثبت و پیگیری سفارش‌ها | کارمندان خدمات پستی | نامه‌رسان‌های پست دولتی | متصدیان تفکیک، توزیع و اپراتورهای ماشین‌های پستی دولتی | کارشناسان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | روسای قطار و مدیران ایستگاه راه‌آهن | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | کارمندان بارگیری، تحویل‌گیری و انبارداری | بازرسان کنترل ناوگان و حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | پیک‌ها و نامه‌رسان‌ها | حق‌العمل‌کاران و کارگزاران گمرکی | متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | رانندگان خودروهای سنگین و کشنده‌ها | رانندگان خودروهای باربری سبک و وانت‌بارها | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | متصدیان ثبت و پیگیری سفارش‌ها | متصدیان باجه و امور پستی | نامه‌رسان‌ها و موزعین پست | اپراتورها و متصدیان تفکیک و پردازش پستی | کارشناسان خرید و امور قراردادها | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | کارمندان انبار، ارسال و دریافت کالا | بازرسان ترابری و حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
